--- a/files/temp_files/statement_2025_03.xlsx
+++ b/files/temp_files/statement_2025_03.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>97.81999999999999</v>
+        <v>-97.81999999999999</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>239.1</v>
+        <v>-239.1</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>49.05</v>
+        <v>-49.05</v>
       </c>
       <c r="D4" t="s">
         <v>61</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>278.5</v>
+        <v>-278.5</v>
       </c>
       <c r="D5" t="s">
         <v>62</v>
@@ -653,7 +653,7 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>353.27</v>
+        <v>-353.27</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
@@ -667,7 +667,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>315.76</v>
+        <v>-315.76</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -681,7 +681,7 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>189.13</v>
+        <v>-189.13</v>
       </c>
       <c r="D8" t="s">
         <v>64</v>
@@ -695,7 +695,7 @@
         <v>42</v>
       </c>
       <c r="C9">
-        <v>8.17</v>
+        <v>-8.17</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -709,7 +709,7 @@
         <v>41</v>
       </c>
       <c r="C10">
-        <v>84.56</v>
+        <v>-84.56</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -723,7 +723,7 @@
         <v>37</v>
       </c>
       <c r="C11">
-        <v>8.15</v>
+        <v>-8.15</v>
       </c>
       <c r="D11" t="s">
         <v>61</v>
@@ -751,7 +751,7 @@
         <v>44</v>
       </c>
       <c r="C13">
-        <v>36.18</v>
+        <v>-36.18</v>
       </c>
       <c r="D13" t="s">
         <v>66</v>
@@ -765,7 +765,7 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>103.18</v>
+        <v>-103.18</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
@@ -779,7 +779,7 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>56.1</v>
+        <v>-56.1</v>
       </c>
       <c r="D15" t="s">
         <v>66</v>
@@ -793,7 +793,7 @@
         <v>47</v>
       </c>
       <c r="C16">
-        <v>44.3</v>
+        <v>-44.3</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -807,7 +807,7 @@
         <v>48</v>
       </c>
       <c r="C17">
-        <v>439.11</v>
+        <v>-439.11</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
@@ -821,7 +821,7 @@
         <v>49</v>
       </c>
       <c r="C18">
-        <v>289.83</v>
+        <v>-289.83</v>
       </c>
       <c r="D18" t="s">
         <v>62</v>
@@ -835,7 +835,7 @@
         <v>50</v>
       </c>
       <c r="C19">
-        <v>70.41</v>
+        <v>-70.41</v>
       </c>
       <c r="D19" t="s">
         <v>64</v>
@@ -849,7 +849,7 @@
         <v>41</v>
       </c>
       <c r="C20">
-        <v>57.44</v>
+        <v>-57.44</v>
       </c>
       <c r="D20" t="s">
         <v>64</v>
@@ -863,7 +863,7 @@
         <v>37</v>
       </c>
       <c r="C21">
-        <v>27.27</v>
+        <v>-27.27</v>
       </c>
       <c r="D21" t="s">
         <v>61</v>
@@ -891,7 +891,7 @@
         <v>49</v>
       </c>
       <c r="C23">
-        <v>249.93</v>
+        <v>-249.93</v>
       </c>
       <c r="D23" t="s">
         <v>62</v>
@@ -905,7 +905,7 @@
         <v>51</v>
       </c>
       <c r="C24">
-        <v>107.08</v>
+        <v>-107.08</v>
       </c>
       <c r="D24" t="s">
         <v>59</v>
@@ -919,7 +919,7 @@
         <v>46</v>
       </c>
       <c r="C25">
-        <v>67.53</v>
+        <v>-67.53</v>
       </c>
       <c r="D25" t="s">
         <v>66</v>
@@ -933,7 +933,7 @@
         <v>49</v>
       </c>
       <c r="C26">
-        <v>222.65</v>
+        <v>-222.65</v>
       </c>
       <c r="D26" t="s">
         <v>62</v>
@@ -947,7 +947,7 @@
         <v>52</v>
       </c>
       <c r="C27">
-        <v>677.46</v>
+        <v>-677.46</v>
       </c>
       <c r="D27" t="s">
         <v>63</v>
@@ -961,7 +961,7 @@
         <v>37</v>
       </c>
       <c r="C28">
-        <v>22.48</v>
+        <v>-22.48</v>
       </c>
       <c r="D28" t="s">
         <v>61</v>
@@ -975,7 +975,7 @@
         <v>42</v>
       </c>
       <c r="C29">
-        <v>36.16</v>
+        <v>-36.16</v>
       </c>
       <c r="D29" t="s">
         <v>61</v>
@@ -989,7 +989,7 @@
         <v>53</v>
       </c>
       <c r="C30">
-        <v>35.29</v>
+        <v>-35.29</v>
       </c>
       <c r="D30" t="s">
         <v>61</v>
@@ -1017,7 +1017,7 @@
         <v>54</v>
       </c>
       <c r="C32">
-        <v>184.28</v>
+        <v>-184.28</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1031,7 +1031,7 @@
         <v>50</v>
       </c>
       <c r="C33">
-        <v>123.91</v>
+        <v>-123.91</v>
       </c>
       <c r="D33" t="s">
         <v>64</v>
@@ -1045,7 +1045,7 @@
         <v>44</v>
       </c>
       <c r="C34">
-        <v>43.94</v>
+        <v>-43.94</v>
       </c>
       <c r="D34" t="s">
         <v>66</v>
@@ -1059,7 +1059,7 @@
         <v>36</v>
       </c>
       <c r="C35">
-        <v>346.5</v>
+        <v>-346.5</v>
       </c>
       <c r="D35" t="s">
         <v>60</v>
@@ -1073,7 +1073,7 @@
         <v>54</v>
       </c>
       <c r="C36">
-        <v>434.31</v>
+        <v>-434.31</v>
       </c>
       <c r="D36" t="s">
         <v>60</v>
@@ -1101,7 +1101,7 @@
         <v>42</v>
       </c>
       <c r="C38">
-        <v>13.94</v>
+        <v>-13.94</v>
       </c>
       <c r="D38" t="s">
         <v>61</v>
@@ -1115,7 +1115,7 @@
         <v>54</v>
       </c>
       <c r="C39">
-        <v>232.25</v>
+        <v>-232.25</v>
       </c>
       <c r="D39" t="s">
         <v>60</v>
@@ -1129,7 +1129,7 @@
         <v>48</v>
       </c>
       <c r="C40">
-        <v>399.1</v>
+        <v>-399.1</v>
       </c>
       <c r="D40" t="s">
         <v>60</v>
@@ -1143,7 +1143,7 @@
         <v>41</v>
       </c>
       <c r="C41">
-        <v>90.2</v>
+        <v>-90.2</v>
       </c>
       <c r="D41" t="s">
         <v>64</v>
@@ -1157,7 +1157,7 @@
         <v>52</v>
       </c>
       <c r="C42">
-        <v>550.6799999999999</v>
+        <v>-550.6799999999999</v>
       </c>
       <c r="D42" t="s">
         <v>63</v>
@@ -1171,7 +1171,7 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>321.28</v>
+        <v>-321.28</v>
       </c>
       <c r="D43" t="s">
         <v>60</v>
@@ -1185,7 +1185,7 @@
         <v>37</v>
       </c>
       <c r="C44">
-        <v>13.7</v>
+        <v>-13.7</v>
       </c>
       <c r="D44" t="s">
         <v>61</v>
@@ -1199,7 +1199,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>45.6</v>
+        <v>-45.6</v>
       </c>
       <c r="D45" t="s">
         <v>66</v>
@@ -1213,7 +1213,7 @@
         <v>48</v>
       </c>
       <c r="C46">
-        <v>158.05</v>
+        <v>-158.05</v>
       </c>
       <c r="D46" t="s">
         <v>60</v>
@@ -1227,7 +1227,7 @@
         <v>44</v>
       </c>
       <c r="C47">
-        <v>77.94</v>
+        <v>-77.94</v>
       </c>
       <c r="D47" t="s">
         <v>66</v>
@@ -1241,7 +1241,7 @@
         <v>37</v>
       </c>
       <c r="C48">
-        <v>26.94</v>
+        <v>-26.94</v>
       </c>
       <c r="D48" t="s">
         <v>61</v>
@@ -1255,7 +1255,7 @@
         <v>40</v>
       </c>
       <c r="C49">
-        <v>906.1799999999999</v>
+        <v>-906.1799999999999</v>
       </c>
       <c r="D49" t="s">
         <v>63</v>
@@ -1269,7 +1269,7 @@
         <v>41</v>
       </c>
       <c r="C50">
-        <v>39.37</v>
+        <v>-39.37</v>
       </c>
       <c r="D50" t="s">
         <v>64</v>
@@ -1283,7 +1283,7 @@
         <v>49</v>
       </c>
       <c r="C51">
-        <v>123.58</v>
+        <v>-123.58</v>
       </c>
       <c r="D51" t="s">
         <v>62</v>
@@ -1297,7 +1297,7 @@
         <v>39</v>
       </c>
       <c r="C52">
-        <v>316.14</v>
+        <v>-316.14</v>
       </c>
       <c r="D52" t="s">
         <v>63</v>
@@ -1311,7 +1311,7 @@
         <v>53</v>
       </c>
       <c r="C53">
-        <v>18.68</v>
+        <v>-18.68</v>
       </c>
       <c r="D53" t="s">
         <v>61</v>
@@ -1325,7 +1325,7 @@
         <v>39</v>
       </c>
       <c r="C54">
-        <v>928.38</v>
+        <v>-928.38</v>
       </c>
       <c r="D54" t="s">
         <v>63</v>
@@ -1339,7 +1339,7 @@
         <v>44</v>
       </c>
       <c r="C55">
-        <v>42.94</v>
+        <v>-42.94</v>
       </c>
       <c r="D55" t="s">
         <v>66</v>
@@ -1353,7 +1353,7 @@
         <v>47</v>
       </c>
       <c r="C56">
-        <v>93.79000000000001</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="D56" t="s">
         <v>66</v>
@@ -1395,7 +1395,7 @@
         <v>45</v>
       </c>
       <c r="C59">
-        <v>39.76</v>
+        <v>-39.76</v>
       </c>
       <c r="D59" t="s">
         <v>59</v>
@@ -1409,7 +1409,7 @@
         <v>51</v>
       </c>
       <c r="C60">
-        <v>38.65</v>
+        <v>-38.65</v>
       </c>
       <c r="D60" t="s">
         <v>59</v>
@@ -1423,7 +1423,7 @@
         <v>51</v>
       </c>
       <c r="C61">
-        <v>149.18</v>
+        <v>-149.18</v>
       </c>
       <c r="D61" t="s">
         <v>59</v>
@@ -1437,7 +1437,7 @@
         <v>35</v>
       </c>
       <c r="C62">
-        <v>129.16</v>
+        <v>-129.16</v>
       </c>
       <c r="D62" t="s">
         <v>59</v>
@@ -1465,7 +1465,7 @@
         <v>46</v>
       </c>
       <c r="C64">
-        <v>65.41</v>
+        <v>-65.41</v>
       </c>
       <c r="D64" t="s">
         <v>66</v>
@@ -1479,7 +1479,7 @@
         <v>54</v>
       </c>
       <c r="C65">
-        <v>391.13</v>
+        <v>-391.13</v>
       </c>
       <c r="D65" t="s">
         <v>60</v>
@@ -1493,7 +1493,7 @@
         <v>35</v>
       </c>
       <c r="C66">
-        <v>93.7</v>
+        <v>-93.7</v>
       </c>
       <c r="D66" t="s">
         <v>59</v>
@@ -1507,7 +1507,7 @@
         <v>51</v>
       </c>
       <c r="C67">
-        <v>124.91</v>
+        <v>-124.91</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1521,7 +1521,7 @@
         <v>37</v>
       </c>
       <c r="C68">
-        <v>3.55</v>
+        <v>-3.55</v>
       </c>
       <c r="D68" t="s">
         <v>61</v>
@@ -1535,7 +1535,7 @@
         <v>42</v>
       </c>
       <c r="C69">
-        <v>39.73</v>
+        <v>-39.73</v>
       </c>
       <c r="D69" t="s">
         <v>61</v>
@@ -1549,7 +1549,7 @@
         <v>52</v>
       </c>
       <c r="C70">
-        <v>807.77</v>
+        <v>-807.77</v>
       </c>
       <c r="D70" t="s">
         <v>63</v>
@@ -1563,7 +1563,7 @@
         <v>39</v>
       </c>
       <c r="C71">
-        <v>909.84</v>
+        <v>-909.84</v>
       </c>
       <c r="D71" t="s">
         <v>63</v>
@@ -1577,7 +1577,7 @@
         <v>42</v>
       </c>
       <c r="C72">
-        <v>32.62</v>
+        <v>-32.62</v>
       </c>
       <c r="D72" t="s">
         <v>61</v>
@@ -1605,7 +1605,7 @@
         <v>52</v>
       </c>
       <c r="C74">
-        <v>477.99</v>
+        <v>-477.99</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -1619,7 +1619,7 @@
         <v>36</v>
       </c>
       <c r="C75">
-        <v>29.28</v>
+        <v>-29.28</v>
       </c>
       <c r="D75" t="s">
         <v>60</v>
@@ -1633,7 +1633,7 @@
         <v>41</v>
       </c>
       <c r="C76">
-        <v>194.5</v>
+        <v>-194.5</v>
       </c>
       <c r="D76" t="s">
         <v>64</v>
@@ -1647,7 +1647,7 @@
         <v>36</v>
       </c>
       <c r="C77">
-        <v>161.61</v>
+        <v>-161.61</v>
       </c>
       <c r="D77" t="s">
         <v>60</v>
@@ -1661,7 +1661,7 @@
         <v>36</v>
       </c>
       <c r="C78">
-        <v>54.67</v>
+        <v>-54.67</v>
       </c>
       <c r="D78" t="s">
         <v>60</v>
@@ -1675,7 +1675,7 @@
         <v>56</v>
       </c>
       <c r="C79">
-        <v>253.27</v>
+        <v>-253.27</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1689,7 +1689,7 @@
         <v>52</v>
       </c>
       <c r="C80">
-        <v>118.78</v>
+        <v>-118.78</v>
       </c>
       <c r="D80" t="s">
         <v>63</v>
@@ -1703,7 +1703,7 @@
         <v>42</v>
       </c>
       <c r="C81">
-        <v>2.48</v>
+        <v>-2.48</v>
       </c>
       <c r="D81" t="s">
         <v>61</v>
@@ -1717,7 +1717,7 @@
         <v>40</v>
       </c>
       <c r="C82">
-        <v>920.96</v>
+        <v>-920.96</v>
       </c>
       <c r="D82" t="s">
         <v>63</v>
@@ -1731,7 +1731,7 @@
         <v>51</v>
       </c>
       <c r="C83">
-        <v>115.25</v>
+        <v>-115.25</v>
       </c>
       <c r="D83" t="s">
         <v>59</v>
@@ -1745,7 +1745,7 @@
         <v>57</v>
       </c>
       <c r="C84">
-        <v>13.99</v>
+        <v>-13.99</v>
       </c>
       <c r="D84" t="s">
         <v>64</v>
@@ -1759,7 +1759,7 @@
         <v>49</v>
       </c>
       <c r="C85">
-        <v>207.83</v>
+        <v>-207.83</v>
       </c>
       <c r="D85" t="s">
         <v>62</v>
@@ -1773,7 +1773,7 @@
         <v>54</v>
       </c>
       <c r="C86">
-        <v>13.56</v>
+        <v>-13.56</v>
       </c>
       <c r="D86" t="s">
         <v>60</v>
@@ -1787,7 +1787,7 @@
         <v>36</v>
       </c>
       <c r="C87">
-        <v>171.68</v>
+        <v>-171.68</v>
       </c>
       <c r="D87" t="s">
         <v>60</v>
@@ -1801,7 +1801,7 @@
         <v>51</v>
       </c>
       <c r="C88">
-        <v>78.44</v>
+        <v>-78.44</v>
       </c>
       <c r="D88" t="s">
         <v>59</v>
@@ -1829,7 +1829,7 @@
         <v>47</v>
       </c>
       <c r="C90">
-        <v>41.26</v>
+        <v>-41.26</v>
       </c>
       <c r="D90" t="s">
         <v>66</v>
@@ -1843,7 +1843,7 @@
         <v>51</v>
       </c>
       <c r="C91">
-        <v>38.32</v>
+        <v>-38.32</v>
       </c>
       <c r="D91" t="s">
         <v>59</v>
@@ -1857,7 +1857,7 @@
         <v>49</v>
       </c>
       <c r="C92">
-        <v>175.38</v>
+        <v>-175.38</v>
       </c>
       <c r="D92" t="s">
         <v>62</v>
@@ -1871,7 +1871,7 @@
         <v>38</v>
       </c>
       <c r="C93">
-        <v>297.03</v>
+        <v>-297.03</v>
       </c>
       <c r="D93" t="s">
         <v>62</v>
@@ -1885,7 +1885,7 @@
         <v>52</v>
       </c>
       <c r="C94">
-        <v>588.7</v>
+        <v>-588.7</v>
       </c>
       <c r="D94" t="s">
         <v>63</v>
@@ -1927,7 +1927,7 @@
         <v>47</v>
       </c>
       <c r="C97">
-        <v>82.75</v>
+        <v>-82.75</v>
       </c>
       <c r="D97" t="s">
         <v>66</v>
@@ -1941,7 +1941,7 @@
         <v>52</v>
       </c>
       <c r="C98">
-        <v>65.78</v>
+        <v>-65.78</v>
       </c>
       <c r="D98" t="s">
         <v>63</v>
@@ -1955,7 +1955,7 @@
         <v>57</v>
       </c>
       <c r="C99">
-        <v>110.81</v>
+        <v>-110.81</v>
       </c>
       <c r="D99" t="s">
         <v>64</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="C100">
-        <v>166.78</v>
+        <v>-166.78</v>
       </c>
       <c r="D100" t="s">
         <v>62</v>
@@ -1983,7 +1983,7 @@
         <v>42</v>
       </c>
       <c r="C101">
-        <v>12.33</v>
+        <v>-12.33</v>
       </c>
       <c r="D101" t="s">
         <v>61</v>
@@ -1997,7 +1997,7 @@
         <v>48</v>
       </c>
       <c r="C102">
-        <v>30.1</v>
+        <v>-30.1</v>
       </c>
       <c r="D102" t="s">
         <v>60</v>
@@ -2011,7 +2011,7 @@
         <v>51</v>
       </c>
       <c r="C103">
-        <v>138.66</v>
+        <v>-138.66</v>
       </c>
       <c r="D103" t="s">
         <v>59</v>
@@ -2025,7 +2025,7 @@
         <v>35</v>
       </c>
       <c r="C104">
-        <v>21.26</v>
+        <v>-21.26</v>
       </c>
       <c r="D104" t="s">
         <v>59</v>
@@ -2039,7 +2039,7 @@
         <v>49</v>
       </c>
       <c r="C105">
-        <v>121.84</v>
+        <v>-121.84</v>
       </c>
       <c r="D105" t="s">
         <v>62</v>
@@ -2053,7 +2053,7 @@
         <v>48</v>
       </c>
       <c r="C106">
-        <v>283.65</v>
+        <v>-283.65</v>
       </c>
       <c r="D106" t="s">
         <v>60</v>
@@ -2067,7 +2067,7 @@
         <v>41</v>
       </c>
       <c r="C107">
-        <v>164.19</v>
+        <v>-164.19</v>
       </c>
       <c r="D107" t="s">
         <v>64</v>
@@ -2081,7 +2081,7 @@
         <v>41</v>
       </c>
       <c r="C108">
-        <v>159.5</v>
+        <v>-159.5</v>
       </c>
       <c r="D108" t="s">
         <v>64</v>
@@ -2095,7 +2095,7 @@
         <v>50</v>
       </c>
       <c r="C109">
-        <v>77.56999999999999</v>
+        <v>-77.56999999999999</v>
       </c>
       <c r="D109" t="s">
         <v>64</v>
@@ -2109,7 +2109,7 @@
         <v>37</v>
       </c>
       <c r="C110">
-        <v>11.38</v>
+        <v>-11.38</v>
       </c>
       <c r="D110" t="s">
         <v>61</v>
@@ -2137,7 +2137,7 @@
         <v>51</v>
       </c>
       <c r="C112">
-        <v>137.54</v>
+        <v>-137.54</v>
       </c>
       <c r="D112" t="s">
         <v>59</v>
@@ -2165,7 +2165,7 @@
         <v>38</v>
       </c>
       <c r="C114">
-        <v>165.97</v>
+        <v>-165.97</v>
       </c>
       <c r="D114" t="s">
         <v>62</v>
@@ -2193,7 +2193,7 @@
         <v>35</v>
       </c>
       <c r="C116">
-        <v>134.19</v>
+        <v>-134.19</v>
       </c>
       <c r="D116" t="s">
         <v>59</v>
@@ -2207,7 +2207,7 @@
         <v>35</v>
       </c>
       <c r="C117">
-        <v>142.17</v>
+        <v>-142.17</v>
       </c>
       <c r="D117" t="s">
         <v>59</v>
@@ -2221,7 +2221,7 @@
         <v>35</v>
       </c>
       <c r="C118">
-        <v>146.14</v>
+        <v>-146.14</v>
       </c>
       <c r="D118" t="s">
         <v>59</v>
@@ -2235,7 +2235,7 @@
         <v>37</v>
       </c>
       <c r="C119">
-        <v>8.01</v>
+        <v>-8.01</v>
       </c>
       <c r="D119" t="s">
         <v>61</v>
@@ -2249,7 +2249,7 @@
         <v>37</v>
       </c>
       <c r="C120">
-        <v>27.57</v>
+        <v>-27.57</v>
       </c>
       <c r="D120" t="s">
         <v>61</v>
@@ -2277,7 +2277,7 @@
         <v>38</v>
       </c>
       <c r="C122">
-        <v>104.05</v>
+        <v>-104.05</v>
       </c>
       <c r="D122" t="s">
         <v>62</v>
@@ -2291,7 +2291,7 @@
         <v>46</v>
       </c>
       <c r="C123">
-        <v>21.67</v>
+        <v>-21.67</v>
       </c>
       <c r="D123" t="s">
         <v>66</v>
@@ -2305,7 +2305,7 @@
         <v>38</v>
       </c>
       <c r="C124">
-        <v>128.41</v>
+        <v>-128.41</v>
       </c>
       <c r="D124" t="s">
         <v>62</v>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
       <c r="C125">
-        <v>987.73</v>
+        <v>-987.73</v>
       </c>
       <c r="D125" t="s">
         <v>63</v>
@@ -2333,7 +2333,7 @@
         <v>53</v>
       </c>
       <c r="C126">
-        <v>3.92</v>
+        <v>-3.92</v>
       </c>
       <c r="D126" t="s">
         <v>61</v>
@@ -2347,7 +2347,7 @@
         <v>39</v>
       </c>
       <c r="C127">
-        <v>895.29</v>
+        <v>-895.29</v>
       </c>
       <c r="D127" t="s">
         <v>63</v>
@@ -2361,7 +2361,7 @@
         <v>42</v>
       </c>
       <c r="C128">
-        <v>46.41</v>
+        <v>-46.41</v>
       </c>
       <c r="D128" t="s">
         <v>61</v>
@@ -2375,7 +2375,7 @@
         <v>57</v>
       </c>
       <c r="C129">
-        <v>166.05</v>
+        <v>-166.05</v>
       </c>
       <c r="D129" t="s">
         <v>64</v>
@@ -2389,7 +2389,7 @@
         <v>49</v>
       </c>
       <c r="C130">
-        <v>166.57</v>
+        <v>-166.57</v>
       </c>
       <c r="D130" t="s">
         <v>62</v>
@@ -2403,7 +2403,7 @@
         <v>52</v>
       </c>
       <c r="C131">
-        <v>110.57</v>
+        <v>-110.57</v>
       </c>
       <c r="D131" t="s">
         <v>63</v>
@@ -2445,7 +2445,7 @@
         <v>46</v>
       </c>
       <c r="C134">
-        <v>40.08</v>
+        <v>-40.08</v>
       </c>
       <c r="D134" t="s">
         <v>66</v>
@@ -2459,7 +2459,7 @@
         <v>45</v>
       </c>
       <c r="C135">
-        <v>106.28</v>
+        <v>-106.28</v>
       </c>
       <c r="D135" t="s">
         <v>59</v>
@@ -2473,7 +2473,7 @@
         <v>52</v>
       </c>
       <c r="C136">
-        <v>35.96</v>
+        <v>-35.96</v>
       </c>
       <c r="D136" t="s">
         <v>63</v>
@@ -2487,7 +2487,7 @@
         <v>44</v>
       </c>
       <c r="C137">
-        <v>93.26000000000001</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="D137" t="s">
         <v>66</v>
@@ -2501,7 +2501,7 @@
         <v>37</v>
       </c>
       <c r="C138">
-        <v>21.56</v>
+        <v>-21.56</v>
       </c>
       <c r="D138" t="s">
         <v>61</v>
@@ -2515,7 +2515,7 @@
         <v>35</v>
       </c>
       <c r="C139">
-        <v>148.05</v>
+        <v>-148.05</v>
       </c>
       <c r="D139" t="s">
         <v>59</v>
@@ -2529,7 +2529,7 @@
         <v>37</v>
       </c>
       <c r="C140">
-        <v>22.15</v>
+        <v>-22.15</v>
       </c>
       <c r="D140" t="s">
         <v>61</v>
@@ -2543,7 +2543,7 @@
         <v>46</v>
       </c>
       <c r="C141">
-        <v>46.48</v>
+        <v>-46.48</v>
       </c>
       <c r="D141" t="s">
         <v>66</v>
@@ -2557,7 +2557,7 @@
         <v>38</v>
       </c>
       <c r="C142">
-        <v>288.19</v>
+        <v>-288.19</v>
       </c>
       <c r="D142" t="s">
         <v>62</v>
@@ -2571,7 +2571,7 @@
         <v>39</v>
       </c>
       <c r="C143">
-        <v>532.41</v>
+        <v>-532.41</v>
       </c>
       <c r="D143" t="s">
         <v>63</v>
@@ -2585,7 +2585,7 @@
         <v>49</v>
       </c>
       <c r="C144">
-        <v>149.96</v>
+        <v>-149.96</v>
       </c>
       <c r="D144" t="s">
         <v>62</v>
@@ -2599,7 +2599,7 @@
         <v>51</v>
       </c>
       <c r="C145">
-        <v>45.85</v>
+        <v>-45.85</v>
       </c>
       <c r="D145" t="s">
         <v>59</v>
@@ -2613,7 +2613,7 @@
         <v>52</v>
       </c>
       <c r="C146">
-        <v>876.87</v>
+        <v>-876.87</v>
       </c>
       <c r="D146" t="s">
         <v>63</v>
@@ -2627,7 +2627,7 @@
         <v>49</v>
       </c>
       <c r="C147">
-        <v>132.9</v>
+        <v>-132.9</v>
       </c>
       <c r="D147" t="s">
         <v>62</v>
@@ -2641,7 +2641,7 @@
         <v>39</v>
       </c>
       <c r="C148">
-        <v>161.83</v>
+        <v>-161.83</v>
       </c>
       <c r="D148" t="s">
         <v>63</v>
@@ -2655,7 +2655,7 @@
         <v>40</v>
       </c>
       <c r="C149">
-        <v>780.3</v>
+        <v>-780.3</v>
       </c>
       <c r="D149" t="s">
         <v>63</v>
@@ -2683,7 +2683,7 @@
         <v>37</v>
       </c>
       <c r="C151">
-        <v>20.94</v>
+        <v>-20.94</v>
       </c>
       <c r="D151" t="s">
         <v>61</v>
@@ -2711,7 +2711,7 @@
         <v>44</v>
       </c>
       <c r="C153">
-        <v>83.73</v>
+        <v>-83.73</v>
       </c>
       <c r="D153" t="s">
         <v>66</v>
@@ -2725,7 +2725,7 @@
         <v>57</v>
       </c>
       <c r="C154">
-        <v>145.24</v>
+        <v>-145.24</v>
       </c>
       <c r="D154" t="s">
         <v>64</v>
@@ -2739,7 +2739,7 @@
         <v>46</v>
       </c>
       <c r="C155">
-        <v>87.08</v>
+        <v>-87.08</v>
       </c>
       <c r="D155" t="s">
         <v>66</v>
@@ -2767,7 +2767,7 @@
         <v>51</v>
       </c>
       <c r="C157">
-        <v>142.57</v>
+        <v>-142.57</v>
       </c>
       <c r="D157" t="s">
         <v>59</v>
@@ -2781,7 +2781,7 @@
         <v>49</v>
       </c>
       <c r="C158">
-        <v>158.65</v>
+        <v>-158.65</v>
       </c>
       <c r="D158" t="s">
         <v>62</v>
@@ -2795,7 +2795,7 @@
         <v>48</v>
       </c>
       <c r="C159">
-        <v>267.93</v>
+        <v>-267.93</v>
       </c>
       <c r="D159" t="s">
         <v>60</v>
@@ -2809,7 +2809,7 @@
         <v>44</v>
       </c>
       <c r="C160">
-        <v>95.70999999999999</v>
+        <v>-95.70999999999999</v>
       </c>
       <c r="D160" t="s">
         <v>66</v>
@@ -2823,7 +2823,7 @@
         <v>50</v>
       </c>
       <c r="C161">
-        <v>171.9</v>
+        <v>-171.9</v>
       </c>
       <c r="D161" t="s">
         <v>64</v>
@@ -2837,7 +2837,7 @@
         <v>44</v>
       </c>
       <c r="C162">
-        <v>74.04000000000001</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="D162" t="s">
         <v>66</v>
@@ -2879,7 +2879,7 @@
         <v>53</v>
       </c>
       <c r="C165">
-        <v>30.1</v>
+        <v>-30.1</v>
       </c>
       <c r="D165" t="s">
         <v>61</v>
@@ -2893,7 +2893,7 @@
         <v>42</v>
       </c>
       <c r="C166">
-        <v>36.67</v>
+        <v>-36.67</v>
       </c>
       <c r="D166" t="s">
         <v>61</v>
@@ -2907,7 +2907,7 @@
         <v>45</v>
       </c>
       <c r="C167">
-        <v>35.49</v>
+        <v>-35.49</v>
       </c>
       <c r="D167" t="s">
         <v>59</v>
@@ -2921,7 +2921,7 @@
         <v>49</v>
       </c>
       <c r="C168">
-        <v>279.58</v>
+        <v>-279.58</v>
       </c>
       <c r="D168" t="s">
         <v>62</v>
@@ -2935,7 +2935,7 @@
         <v>39</v>
       </c>
       <c r="C169">
-        <v>988.91</v>
+        <v>-988.91</v>
       </c>
       <c r="D169" t="s">
         <v>63</v>
@@ -2949,7 +2949,7 @@
         <v>49</v>
       </c>
       <c r="C170">
-        <v>81.20999999999999</v>
+        <v>-81.20999999999999</v>
       </c>
       <c r="D170" t="s">
         <v>62</v>
@@ -2963,7 +2963,7 @@
         <v>53</v>
       </c>
       <c r="C171">
-        <v>40.58</v>
+        <v>-40.58</v>
       </c>
       <c r="D171" t="s">
         <v>61</v>
@@ -2991,7 +2991,7 @@
         <v>52</v>
       </c>
       <c r="C173">
-        <v>632.91</v>
+        <v>-632.91</v>
       </c>
       <c r="D173" t="s">
         <v>63</v>
@@ -3005,7 +3005,7 @@
         <v>42</v>
       </c>
       <c r="C174">
-        <v>32.94</v>
+        <v>-32.94</v>
       </c>
       <c r="D174" t="s">
         <v>61</v>
@@ -3019,7 +3019,7 @@
         <v>44</v>
       </c>
       <c r="C175">
-        <v>13.98</v>
+        <v>-13.98</v>
       </c>
       <c r="D175" t="s">
         <v>66</v>
@@ -3047,7 +3047,7 @@
         <v>35</v>
       </c>
       <c r="C177">
-        <v>125.07</v>
+        <v>-125.07</v>
       </c>
       <c r="D177" t="s">
         <v>59</v>
@@ -3061,7 +3061,7 @@
         <v>35</v>
       </c>
       <c r="C178">
-        <v>87.68000000000001</v>
+        <v>-87.68000000000001</v>
       </c>
       <c r="D178" t="s">
         <v>59</v>
@@ -3075,7 +3075,7 @@
         <v>54</v>
       </c>
       <c r="C179">
-        <v>317.25</v>
+        <v>-317.25</v>
       </c>
       <c r="D179" t="s">
         <v>60</v>
@@ -3089,7 +3089,7 @@
         <v>40</v>
       </c>
       <c r="C180">
-        <v>349.54</v>
+        <v>-349.54</v>
       </c>
       <c r="D180" t="s">
         <v>63</v>
@@ -3103,7 +3103,7 @@
         <v>45</v>
       </c>
       <c r="C181">
-        <v>27.89</v>
+        <v>-27.89</v>
       </c>
       <c r="D181" t="s">
         <v>59</v>
@@ -3117,7 +3117,7 @@
         <v>41</v>
       </c>
       <c r="C182">
-        <v>107.51</v>
+        <v>-107.51</v>
       </c>
       <c r="D182" t="s">
         <v>64</v>
@@ -3131,7 +3131,7 @@
         <v>36</v>
       </c>
       <c r="C183">
-        <v>360.68</v>
+        <v>-360.68</v>
       </c>
       <c r="D183" t="s">
         <v>60</v>
@@ -3145,7 +3145,7 @@
         <v>54</v>
       </c>
       <c r="C184">
-        <v>5.68</v>
+        <v>-5.68</v>
       </c>
       <c r="D184" t="s">
         <v>60</v>
@@ -3159,7 +3159,7 @@
         <v>38</v>
       </c>
       <c r="C185">
-        <v>103.88</v>
+        <v>-103.88</v>
       </c>
       <c r="D185" t="s">
         <v>62</v>
@@ -3173,7 +3173,7 @@
         <v>37</v>
       </c>
       <c r="C186">
-        <v>20.12</v>
+        <v>-20.12</v>
       </c>
       <c r="D186" t="s">
         <v>61</v>
@@ -3187,7 +3187,7 @@
         <v>51</v>
       </c>
       <c r="C187">
-        <v>149.83</v>
+        <v>-149.83</v>
       </c>
       <c r="D187" t="s">
         <v>59</v>
@@ -3201,7 +3201,7 @@
         <v>44</v>
       </c>
       <c r="C188">
-        <v>68.79000000000001</v>
+        <v>-68.79000000000001</v>
       </c>
       <c r="D188" t="s">
         <v>66</v>
@@ -3215,7 +3215,7 @@
         <v>49</v>
       </c>
       <c r="C189">
-        <v>260.94</v>
+        <v>-260.94</v>
       </c>
       <c r="D189" t="s">
         <v>62</v>
@@ -3229,7 +3229,7 @@
         <v>52</v>
       </c>
       <c r="C190">
-        <v>798.6900000000001</v>
+        <v>-798.6900000000001</v>
       </c>
       <c r="D190" t="s">
         <v>63</v>
@@ -3243,7 +3243,7 @@
         <v>35</v>
       </c>
       <c r="C191">
-        <v>57.32</v>
+        <v>-57.32</v>
       </c>
       <c r="D191" t="s">
         <v>59</v>
@@ -3257,7 +3257,7 @@
         <v>36</v>
       </c>
       <c r="C192">
-        <v>270.05</v>
+        <v>-270.05</v>
       </c>
       <c r="D192" t="s">
         <v>60</v>
@@ -3271,7 +3271,7 @@
         <v>36</v>
       </c>
       <c r="C193">
-        <v>177.02</v>
+        <v>-177.02</v>
       </c>
       <c r="D193" t="s">
         <v>60</v>
@@ -3285,7 +3285,7 @@
         <v>53</v>
       </c>
       <c r="C194">
-        <v>44.33</v>
+        <v>-44.33</v>
       </c>
       <c r="D194" t="s">
         <v>61</v>
@@ -3299,7 +3299,7 @@
         <v>48</v>
       </c>
       <c r="C195">
-        <v>366.17</v>
+        <v>-366.17</v>
       </c>
       <c r="D195" t="s">
         <v>60</v>
@@ -3313,7 +3313,7 @@
         <v>47</v>
       </c>
       <c r="C196">
-        <v>53.29</v>
+        <v>-53.29</v>
       </c>
       <c r="D196" t="s">
         <v>66</v>
@@ -3327,7 +3327,7 @@
         <v>42</v>
       </c>
       <c r="C197">
-        <v>19.82</v>
+        <v>-19.82</v>
       </c>
       <c r="D197" t="s">
         <v>61</v>
@@ -3341,7 +3341,7 @@
         <v>52</v>
       </c>
       <c r="C198">
-        <v>204.94</v>
+        <v>-204.94</v>
       </c>
       <c r="D198" t="s">
         <v>63</v>
@@ -3355,7 +3355,7 @@
         <v>56</v>
       </c>
       <c r="C199">
-        <v>65.84</v>
+        <v>-65.84</v>
       </c>
       <c r="D199" t="s">
         <v>62</v>
@@ -3369,7 +3369,7 @@
         <v>54</v>
       </c>
       <c r="C200">
-        <v>296.97</v>
+        <v>-296.97</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
@@ -3383,7 +3383,7 @@
         <v>35</v>
       </c>
       <c r="C201">
-        <v>148.33</v>
+        <v>-148.33</v>
       </c>
       <c r="D201" t="s">
         <v>59</v>
